--- a/src/test/resources/teda/xlsx/MULTIPLE_TABLES_IN_ONE_SHEET.xlsx
+++ b/src/test/resources/teda/xlsx/MULTIPLE_TABLES_IN_ONE_SHEET.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10719"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/patrick/Projects/teda-framework/src/test/resources/teda/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\teda-framework\src\test\resources\teda\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6083DA72-B998-8D48-B15D-CDD8F5C473D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D6153C7-60CF-49F6-861A-AF2B02890246}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="25820" windowHeight="20340" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22640" yWindow="2880" windowWidth="25760" windowHeight="12940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cockpit" sheetId="1" r:id="rId1"/>
@@ -147,17 +147,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -207,8 +204,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="C4:F6" totalsRowShown="0">
-  <autoFilter ref="C4:F6" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="B3:E5" totalsRowShown="0">
+  <autoFilter ref="B3:E5" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="TRUNCATE"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="LOAD"/>
@@ -220,8 +217,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Table13578" displayName="Table13578" ref="C4:F8" totalsRowShown="0">
-  <autoFilter ref="C4:F8" xr:uid="{00000000-0009-0000-0100-000007000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Table13578" displayName="Table13578" ref="B3:E7" totalsRowShown="0">
+  <autoFilter ref="B3:E7" xr:uid="{00000000-0009-0000-0100-000007000000}"/>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="#ID" dataDxfId="9"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="NAME" dataDxfId="8"/>
@@ -233,8 +230,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{F9CD9E30-F464-634D-B9CC-F1BC91B7FEA8}" name="Table135783" displayName="Table135783" ref="C11:F15" totalsRowShown="0">
-  <autoFilter ref="C11:F15" xr:uid="{F9CD9E30-F464-634D-B9CC-F1BC91B7FEA8}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{F9CD9E30-F464-634D-B9CC-F1BC91B7FEA8}" name="Table135783" displayName="Table135783" ref="B10:E14" totalsRowShown="0">
+  <autoFilter ref="B10:E14" xr:uid="{F9CD9E30-F464-634D-B9CC-F1BC91B7FEA8}"/>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{E3B5017E-96D8-6A48-BAB0-36B8D8FC37E8}" name="#ID" dataDxfId="7"/>
     <tableColumn id="2" xr3:uid="{834A28C9-8705-AD44-AAA8-C205E2253100}" name="NAME" dataDxfId="6"/>
@@ -246,8 +243,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Table4" displayName="Table4" ref="C4:F8">
-  <autoFilter ref="C4:F8" xr:uid="{00000000-0009-0000-0100-000004000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Table4" displayName="Table4" ref="B3:E7">
+  <autoFilter ref="B3:E7" xr:uid="{00000000-0009-0000-0100-000004000000}"/>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="#ID" totalsRowLabel="Ergebnis" dataDxfId="5"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="NAME" dataDxfId="4"/>
@@ -259,8 +256,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{CE5CFC1B-2E57-7645-B02B-2F7B81784059}" name="Table44" displayName="Table44" ref="C11:F15">
-  <autoFilter ref="C11:F15" xr:uid="{CE5CFC1B-2E57-7645-B02B-2F7B81784059}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{CE5CFC1B-2E57-7645-B02B-2F7B81784059}" name="Table44" displayName="Table44" ref="B10:E14">
+  <autoFilter ref="B10:E14" xr:uid="{CE5CFC1B-2E57-7645-B02B-2F7B81784059}"/>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{2ADFE462-C6A8-4242-85D8-992F4DF6A472}" name="#ID" totalsRowLabel="Ergebnis" dataDxfId="2"/>
     <tableColumn id="2" xr3:uid="{8C38C0F2-429F-CC4A-B256-6CEBE3322318}" name="NAME" dataDxfId="1"/>
@@ -561,62 +558,65 @@
   <sheetPr>
     <tabColor rgb="FFC00000"/>
   </sheetPr>
-  <dimension ref="B3:F10"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="B2:E10"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="12.1640625" customWidth="1"/>
-    <col min="3" max="6" width="34.33203125" customWidth="1"/>
+    <col min="2" max="2" width="13.7265625" customWidth="1"/>
+    <col min="3" max="3" width="20.08984375" customWidth="1"/>
+    <col min="4" max="4" width="17.90625" customWidth="1"/>
+    <col min="5" max="5" width="17.453125" customWidth="1"/>
+    <col min="6" max="6" width="34.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B3" s="1" t="s">
+    <row r="2" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B2" s="6" t="s">
         <v>0</v>
       </c>
+      <c r="C2" s="6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B3" t="s">
+        <v>2</v>
+      </c>
       <c r="C3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="C4" t="s">
-        <v>2</v>
-      </c>
-      <c r="D4" t="s">
         <v>3</v>
       </c>
-      <c r="E4" t="s">
+      <c r="D3" t="s">
         <v>4</v>
       </c>
-      <c r="F4" t="s">
+      <c r="E3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B5" t="s">
+        <v>23</v>
+      </c>
       <c r="C5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="C6" t="s">
-        <v>23</v>
-      </c>
-      <c r="D6" t="s">
         <v>12</v>
       </c>
-      <c r="E6" t="s">
+      <c r="D5" t="s">
         <v>22</v>
       </c>
-      <c r="F6" t="s">
+      <c r="E5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="E8" s="3"/>
-    </row>
-    <row r="9" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="E9" s="3"/>
-    </row>
-    <row r="10" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="E10" s="3"/>
+    <row r="8" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="E8" s="2"/>
+    </row>
+    <row r="9" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="E9" s="2"/>
+    </row>
+    <row r="10" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="E10" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -633,201 +633,197 @@
   <sheetPr>
     <tabColor rgb="FF0070C0"/>
   </sheetPr>
-  <dimension ref="B3:F19"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="B2:E19"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="13.6640625" customWidth="1"/>
-    <col min="3" max="3" width="20.5" customWidth="1"/>
-    <col min="4" max="4" width="21.83203125" customWidth="1"/>
-    <col min="5" max="5" width="21.6640625" customWidth="1"/>
+    <col min="2" max="2" width="13.6328125" customWidth="1"/>
+    <col min="3" max="3" width="20.453125" customWidth="1"/>
+    <col min="4" max="4" width="21.81640625" customWidth="1"/>
+    <col min="5" max="5" width="21.6328125" customWidth="1"/>
     <col min="6" max="6" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B3" s="1" t="s">
+    <row r="2" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="7"/>
-      <c r="E3" s="7"/>
-    </row>
-    <row r="4" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="C4" t="s">
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+    </row>
+    <row r="3" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B3" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="C3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E4" t="s">
+      <c r="D3" t="s">
         <v>15</v>
       </c>
-      <c r="F4" t="s">
+      <c r="E3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="C5" s="2" t="s">
+    <row r="4" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="C4" s="1" t="s">
         <v>17</v>
       </c>
+      <c r="D4">
+        <v>22</v>
+      </c>
+      <c r="E4">
+        <v>12.66</v>
+      </c>
+    </row>
+    <row r="5" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5">
+        <v>45</v>
+      </c>
       <c r="E5">
+        <v>34.44</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6">
+        <v>21</v>
+      </c>
+      <c r="E6">
+        <v>24.33</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7">
+        <v>66</v>
+      </c>
+      <c r="E7" s="5">
+        <v>4.3939494940000001</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
+    </row>
+    <row r="9" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B9" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+    </row>
+    <row r="10" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B10" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D10" t="s">
+        <v>15</v>
+      </c>
+      <c r="E10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B11" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D11">
         <v>22</v>
       </c>
-      <c r="F5">
+      <c r="E11">
         <v>12.66</v>
       </c>
     </row>
-    <row r="6" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="C6" s="2" t="s">
+    <row r="12" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="C12" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E6">
+      <c r="D12">
         <v>45</v>
       </c>
-      <c r="F6">
+      <c r="E12">
         <v>34.44</v>
       </c>
     </row>
-    <row r="7" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="C7" s="2" t="s">
+    <row r="13" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B13" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="C13" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E7">
+      <c r="D13">
         <v>21</v>
       </c>
-      <c r="F7">
+      <c r="E13">
         <v>24.33</v>
       </c>
     </row>
-    <row r="8" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="C8" s="2" t="s">
+    <row r="14" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B14" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="C14" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E8">
+      <c r="D14">
         <v>66</v>
       </c>
-      <c r="F8" s="6">
+      <c r="E14" s="5">
         <v>4.3939494940000001</v>
       </c>
     </row>
-    <row r="9" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-    </row>
-    <row r="10" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B10" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
-    </row>
-    <row r="11" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="C11" t="s">
-        <v>21</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E11" t="s">
-        <v>15</v>
-      </c>
-      <c r="F11" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="12" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="C12" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E12">
-        <v>22</v>
-      </c>
-      <c r="F12">
-        <v>12.66</v>
-      </c>
-    </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="C13" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E13">
-        <v>45</v>
-      </c>
-      <c r="F13">
-        <v>34.44</v>
-      </c>
-    </row>
-    <row r="14" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="C14" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E14">
-        <v>21</v>
-      </c>
-      <c r="F14">
-        <v>24.33</v>
-      </c>
-    </row>
-    <row r="15" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="C15" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15">
-        <v>66</v>
-      </c>
-      <c r="F15" s="6">
-        <v>4.3939494940000001</v>
-      </c>
-    </row>
-    <row r="16" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-    </row>
-    <row r="17" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
-    </row>
-    <row r="18" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
-    </row>
-    <row r="19" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
+    <row r="16" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="C16" s="1"/>
+      <c r="D16" s="1"/>
+    </row>
+    <row r="17" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
+    </row>
+    <row r="18" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
+    </row>
+    <row r="19" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="C3:E3"/>
-    <mergeCell ref="C10:E10"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="2">
     <tablePart r:id="rId1"/>
@@ -841,174 +837,174 @@
   <sheetPr>
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="B3:F15"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="B2:F14"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="14.5" customWidth="1"/>
-    <col min="3" max="3" width="26.33203125" customWidth="1"/>
-    <col min="4" max="4" width="32.5" customWidth="1"/>
-    <col min="5" max="5" width="29.83203125" customWidth="1"/>
-    <col min="6" max="6" width="36.33203125" customWidth="1"/>
+    <col min="2" max="2" width="14.453125" customWidth="1"/>
+    <col min="3" max="3" width="26.36328125" customWidth="1"/>
+    <col min="4" max="4" width="32.453125" customWidth="1"/>
+    <col min="5" max="5" width="29.81640625" customWidth="1"/>
+    <col min="6" max="6" width="36.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B3" s="1" t="s">
+    <row r="2" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C2" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="C4" t="s">
+    <row r="3" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B3" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="C3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E4" t="s">
+      <c r="D3" t="s">
         <v>15</v>
       </c>
-      <c r="F4" t="s">
+      <c r="E3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="C5" s="2" t="s">
+    <row r="4" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="C4" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E5">
+      <c r="D4">
         <v>22</v>
       </c>
-      <c r="F5" s="4">
+      <c r="E4" s="3">
         <v>12.66</v>
       </c>
     </row>
-    <row r="6" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="C6" s="2" t="s">
+    <row r="5" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="C5" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E6">
+      <c r="D5">
         <v>45</v>
       </c>
-      <c r="F6" s="4">
+      <c r="E5" s="3">
         <v>34.44</v>
       </c>
     </row>
-    <row r="7" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="C7" s="2" t="s">
+    <row r="6" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B6" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="C6" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E7">
+      <c r="D6">
         <v>21</v>
       </c>
-      <c r="F7" s="4">
+      <c r="E6" s="3">
         <v>24.33</v>
       </c>
     </row>
-    <row r="8" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="C8" s="2" t="s">
+    <row r="7" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="C7" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E8">
+      <c r="D7">
         <v>66</v>
       </c>
-      <c r="F8" s="5">
+      <c r="E7" s="4">
         <v>4.3939494940000001</v>
       </c>
     </row>
-    <row r="9" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="F9" s="2"/>
-    </row>
-    <row r="10" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B10" s="1" t="s">
+    <row r="8" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
+    </row>
+    <row r="9" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B9" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C9" s="2" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="11" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="C11" t="s">
+      <c r="F9" s="1"/>
+    </row>
+    <row r="10" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B10" t="s">
         <v>21</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="C10" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E11" t="s">
+      <c r="D10" t="s">
         <v>15</v>
       </c>
-      <c r="F11" t="s">
+      <c r="E10" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="C12" s="2" t="s">
+    <row r="11" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B11" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="C11" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E12">
+      <c r="D11">
         <v>22</v>
       </c>
-      <c r="F12" s="4">
+      <c r="E11" s="3">
         <v>12.66</v>
       </c>
     </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="C13" s="2" t="s">
+    <row r="12" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="C12" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E13">
+      <c r="D12">
         <v>45</v>
       </c>
-      <c r="F13" s="4">
+      <c r="E12" s="3">
         <v>34.44</v>
       </c>
     </row>
-    <row r="14" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="C14" s="2" t="s">
+    <row r="13" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B13" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="C13" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E14">
+      <c r="D13">
         <v>21</v>
       </c>
-      <c r="F14" s="4">
+      <c r="E13" s="3">
         <v>24.33</v>
       </c>
     </row>
-    <row r="15" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="C15" s="2" t="s">
+    <row r="14" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B14" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="C14" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E15">
+      <c r="D14">
         <v>66</v>
       </c>
-      <c r="F15" s="5">
+      <c r="E14" s="4">
         <v>4.3939494940000001</v>
       </c>
     </row>
